--- a/output/details/2026-05-21/preprocessed_data.xlsx
+++ b/output/details/2026-05-21/preprocessed_data.xlsx
@@ -15231,25 +15231,25 @@
         <v>46163</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.1133411474493728</v>
+        <v>-0.1172766886190473</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1562639050940814</v>
+        <v>-0.1393889393649188</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1560485023436993</v>
+        <v>-0.1391152109626127</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.1215491745863754</v>
+        <v>0.003109272383721144</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001699477607195917</v>
+        <v>0.001696421285509035</v>
       </c>
       <c r="G2" t="n">
-        <v>1.919044138056863</v>
+        <v>2.484077061227512</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.4432316253367276</v>
+        <v>-0.2687668365317185</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
